--- a/artfynd/A 22375-2024 artfynd.xlsx
+++ b/artfynd/A 22375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72688991</v>
+        <v>604467</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1562</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Stortimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Thymus pulegioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,34 +703,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåshålet, infarten till tippen 500 m SO om (nära Österbybruk), Upl</t>
+          <t>Blåshålet, 550 m SO om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661697.8976255255</v>
+        <v>661732</v>
       </c>
       <c r="R2" t="n">
-        <v>6675000.934280928</v>
+        <v>6675023</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,29 +738,24 @@
           <t>Film</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-C-Öst-0095</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:41</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:55</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca 20 ex.</t>
+          <t>6675555-1617155</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,21 +769,272 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägren, körväg</t>
+          <t>Gammal och nyaktiverad soptipp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>606955</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107514</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stortimjan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Thymus pulegioides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåshålet, 500 m SO-ut, infarten till tippen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>661741</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6675036</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2007-08-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2007-08-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72688991</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blåshålet, infarten till tippen 500 m SO om (nära Österbybruk), Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>661698</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6675001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-08-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-08-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägren, körväg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22375-2024 artfynd.xlsx
+++ b/artfynd/A 22375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/604467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/606955</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134839324</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,8 +1190,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72688991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>